--- a/data/Marfan.xlsx
+++ b/data/Marfan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chloe/Documents/Projet_ADM/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68C76F42-721D-814A-A9C4-A8D6337B44F2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0AA8FDA-7439-084B-B771-F12FC2BAC0C8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="14">
   <si>
     <t>ID</t>
   </si>
@@ -42,25 +42,7 @@
     <t>age</t>
   </si>
   <si>
-    <t>Exclu de l'analyse statistique</t>
-  </si>
-  <si>
     <t>weight_kg</t>
-  </si>
-  <si>
-    <t>VO2_SV1__percent_theoretical = VAT</t>
-  </si>
-  <si>
-    <t>Fichier à mettre au format long pour certains graphiques</t>
-  </si>
-  <si>
-    <t>Auto questionnaire Pedqsl</t>
-  </si>
-  <si>
-    <t>Periode avant T-3</t>
-  </si>
-  <si>
-    <t>Periode apres T6</t>
   </si>
   <si>
     <t>height_cm</t>
@@ -169,7 +151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -205,7 +187,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -227,8 +208,6 @@
     <xf numFmtId="1" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -530,35 +509,35 @@
       <c r="B1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="L1" s="18" t="s">
         <v>13</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K1" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="L1" s="19" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.2">
@@ -568,7 +547,7 @@
       <c r="B2" s="5">
         <v>10.529774127310061</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="14" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="5">
@@ -592,10 +571,10 @@
       <c r="J2" s="6">
         <v>39.958706632747109</v>
       </c>
-      <c r="K2" s="17">
+      <c r="K2" s="16">
         <v>69.565217391304344</v>
       </c>
-      <c r="L2" s="17">
+      <c r="L2" s="16">
         <v>75</v>
       </c>
     </row>
@@ -606,7 +585,7 @@
       <c r="B3" s="10">
         <v>14.351813826146476</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="15" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="10">
@@ -626,10 +605,10 @@
         <v>38.74224312653152</v>
       </c>
       <c r="J3" s="11"/>
-      <c r="K3" s="20">
+      <c r="K3" s="19">
         <v>86.956521739130437</v>
       </c>
-      <c r="L3" s="20"/>
+      <c r="L3" s="19"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="9">
@@ -638,7 +617,7 @@
       <c r="B4" s="10">
         <v>10.704996577686517</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="15" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="10">
@@ -662,10 +641,10 @@
       <c r="J4" s="11">
         <v>41.531481990651635</v>
       </c>
-      <c r="K4" s="20">
+      <c r="K4" s="19">
         <v>92.391304347826093</v>
       </c>
-      <c r="L4" s="20">
+      <c r="L4" s="19">
         <v>92.391304347826093</v>
       </c>
     </row>
@@ -676,7 +655,7 @@
       <c r="B5" s="5">
         <v>17.393566050650239</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="14" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="5">
@@ -700,10 +679,10 @@
       <c r="J5" s="6">
         <v>45.052754116732331</v>
       </c>
-      <c r="K5" s="17">
+      <c r="K5" s="16">
         <v>52.173913043478258</v>
       </c>
-      <c r="L5" s="17">
+      <c r="L5" s="16">
         <v>57.608695652173914</v>
       </c>
     </row>
@@ -714,7 +693,7 @@
       <c r="B6" s="10">
         <v>18.986995208761122</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="15" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="10">
@@ -734,10 +713,10 @@
         <v>39.959154936144614</v>
       </c>
       <c r="J6" s="11"/>
-      <c r="K6" s="20">
+      <c r="K6" s="19">
         <v>76.086956521739125</v>
       </c>
-      <c r="L6" s="20">
+      <c r="L6" s="19">
         <v>70.652173913043484</v>
       </c>
     </row>
@@ -748,7 +727,7 @@
       <c r="B7" s="5">
         <v>15.36208076659822</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="14" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="5">
@@ -772,10 +751,10 @@
       <c r="J7" s="6">
         <v>52.530344959859711</v>
       </c>
-      <c r="K7" s="17">
+      <c r="K7" s="16">
         <v>86.956521739130437</v>
       </c>
-      <c r="L7" s="17">
+      <c r="L7" s="16">
         <v>95.652173913043484</v>
       </c>
     </row>
@@ -786,7 +765,7 @@
       <c r="B8" s="10">
         <v>12.284736481861739</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="15" t="s">
         <v>2</v>
       </c>
       <c r="D8" s="10">
@@ -806,10 +785,10 @@
         <v>32.16414908013607</v>
       </c>
       <c r="J8" s="11"/>
-      <c r="K8" s="20">
+      <c r="K8" s="19">
         <v>75</v>
       </c>
-      <c r="L8" s="20"/>
+      <c r="L8" s="19"/>
     </row>
     <row r="9" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
@@ -818,7 +797,7 @@
       <c r="B9" s="5">
         <v>12.7419575633128</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="14" t="s">
         <v>2</v>
       </c>
       <c r="D9" s="5">
@@ -842,10 +821,10 @@
       <c r="J9" s="6">
         <v>36.911577069430813</v>
       </c>
-      <c r="K9" s="17">
+      <c r="K9" s="16">
         <v>66.304347826086953</v>
       </c>
-      <c r="L9" s="17">
+      <c r="L9" s="16">
         <v>82.608695652173907</v>
       </c>
     </row>
@@ -856,7 +835,7 @@
       <c r="B10" s="5">
         <v>13.481177275838467</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="14" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="5">
@@ -880,10 +859,10 @@
       <c r="J10" s="6">
         <v>47.335512358429426</v>
       </c>
-      <c r="K10" s="17">
+      <c r="K10" s="16">
         <v>66.304347826086953</v>
       </c>
-      <c r="L10" s="17">
+      <c r="L10" s="16">
         <v>88.043478260869563</v>
       </c>
     </row>
@@ -894,7 +873,7 @@
       <c r="B11" s="5">
         <v>11.321013004791238</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="14" t="s">
         <v>2</v>
       </c>
       <c r="D11" s="5">
@@ -918,10 +897,10 @@
       <c r="J11" s="6">
         <v>42.590756436910283</v>
       </c>
-      <c r="K11" s="17">
+      <c r="K11" s="16">
         <v>92.391304347826093</v>
       </c>
-      <c r="L11" s="17">
+      <c r="L11" s="16">
         <v>97.826086956521735</v>
       </c>
     </row>
@@ -932,7 +911,7 @@
       <c r="B12" s="5">
         <v>8.0876112251882279</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="14" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="5">
@@ -956,10 +935,10 @@
       <c r="J12" s="6">
         <v>53.811381029549729</v>
       </c>
-      <c r="K12" s="17">
+      <c r="K12" s="16">
         <v>84.782608695652172</v>
       </c>
-      <c r="L12" s="17">
+      <c r="L12" s="16">
         <v>92.391304347826093</v>
       </c>
     </row>
@@ -970,7 +949,7 @@
       <c r="B13" s="10">
         <v>14.231348391512663</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="15" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="10">
@@ -990,10 +969,10 @@
         <v>56.480397155808568</v>
       </c>
       <c r="J13" s="11"/>
-      <c r="K13" s="20">
+      <c r="K13" s="19">
         <v>91.304347826086953</v>
       </c>
-      <c r="L13" s="20">
+      <c r="L13" s="19">
         <v>75</v>
       </c>
     </row>
@@ -1004,7 +983,7 @@
       <c r="B14" s="5">
         <v>13.070499657768652</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="14" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="5">
@@ -1028,10 +1007,10 @@
       <c r="J14" s="6">
         <v>31.070821638848635</v>
       </c>
-      <c r="K14" s="17">
+      <c r="K14" s="16">
         <v>68.478260869565219</v>
       </c>
-      <c r="L14" s="17">
+      <c r="L14" s="16">
         <v>73.913043478260875</v>
       </c>
     </row>
@@ -1042,7 +1021,7 @@
       <c r="B15" s="5">
         <v>10.255989048596852</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="14" t="s">
         <v>2</v>
       </c>
       <c r="D15" s="5">
@@ -1066,10 +1045,10 @@
       <c r="J15" s="6">
         <v>49.054142204827144</v>
       </c>
-      <c r="K15" s="17">
+      <c r="K15" s="16">
         <v>81.521739130434781</v>
       </c>
-      <c r="L15" s="17">
+      <c r="L15" s="16">
         <v>72.826086956521735</v>
       </c>
     </row>
@@ -1080,7 +1059,7 @@
       <c r="B16" s="5">
         <v>7.8631074606433948</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="14" t="s">
         <v>2</v>
       </c>
       <c r="D16" s="5">
@@ -1104,10 +1083,10 @@
       <c r="J16" s="6">
         <v>42.815507286224914</v>
       </c>
-      <c r="K16" s="17">
+      <c r="K16" s="16">
         <v>82.608695652173907</v>
       </c>
-      <c r="L16" s="17">
+      <c r="L16" s="16">
         <v>86.956521739130437</v>
       </c>
     </row>
@@ -1118,7 +1097,7 @@
       <c r="B17" s="10">
         <v>10.009582477754963</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="15" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="10">
@@ -1138,10 +1117,10 @@
         <v>40.46344303566898</v>
       </c>
       <c r="J17" s="11"/>
-      <c r="K17" s="20">
+      <c r="K17" s="19">
         <v>83.695652173913047</v>
       </c>
-      <c r="L17" s="20"/>
+      <c r="L17" s="19"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="9">
@@ -1150,7 +1129,7 @@
       <c r="B18" s="10">
         <v>11.143052703627653</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="15" t="s">
         <v>2</v>
       </c>
       <c r="D18" s="10">
@@ -1170,10 +1149,10 @@
         <v>38.62008136227815</v>
       </c>
       <c r="J18" s="11"/>
-      <c r="K18" s="20">
+      <c r="K18" s="19">
         <v>46.739130434782609</v>
       </c>
-      <c r="L18" s="20"/>
+      <c r="L18" s="19"/>
     </row>
     <row r="19" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
@@ -1182,7 +1161,7 @@
       <c r="B19" s="5">
         <v>17.130732375085557</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="14" t="s">
         <v>2</v>
       </c>
       <c r="D19" s="5">
@@ -1206,10 +1185,10 @@
       <c r="J19" s="6">
         <v>25.568107528568813</v>
       </c>
-      <c r="K19" s="17">
+      <c r="K19" s="16">
         <v>65.217391304347828</v>
       </c>
-      <c r="L19" s="17">
+      <c r="L19" s="16">
         <v>77.173913043478265</v>
       </c>
     </row>
@@ -1220,7 +1199,7 @@
       <c r="B20" s="5">
         <v>7.8247775496235459</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="14" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="5">
@@ -1244,10 +1223,10 @@
       <c r="J20" s="6">
         <v>41.160007015287484</v>
       </c>
-      <c r="K20" s="17">
+      <c r="K20" s="16">
         <v>93.478260869565219</v>
       </c>
-      <c r="L20" s="17">
+      <c r="L20" s="16">
         <v>89.130434782608702</v>
       </c>
     </row>
@@ -1258,7 +1237,7 @@
       <c r="B21" s="5">
         <v>10.250513347022586</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="14" t="s">
         <v>2</v>
       </c>
       <c r="D21" s="5">
@@ -1282,10 +1261,10 @@
       <c r="J21" s="6">
         <v>46.919406966603397</v>
       </c>
-      <c r="K21" s="17">
+      <c r="K21" s="16">
         <v>60.869565217391305</v>
       </c>
-      <c r="L21" s="17">
+      <c r="L21" s="16">
         <v>64.130434782608702</v>
       </c>
     </row>
@@ -1296,7 +1275,7 @@
       <c r="B22" s="5">
         <v>11.047227926078028</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C22" s="14" t="s">
         <v>2</v>
       </c>
       <c r="D22" s="5">
@@ -1320,10 +1299,10 @@
       <c r="J22" s="6">
         <v>39.779845152280622</v>
       </c>
-      <c r="K22" s="17">
+      <c r="K22" s="16">
         <v>68.478260869565219</v>
       </c>
-      <c r="L22" s="17">
+      <c r="L22" s="16">
         <v>83.695652173913047</v>
       </c>
     </row>
@@ -1334,7 +1313,7 @@
       <c r="B23" s="5">
         <v>17.828884325804243</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="14" t="s">
         <v>2</v>
       </c>
       <c r="D23" s="5">
@@ -1358,10 +1337,10 @@
       <c r="J23" s="6">
         <v>39.362415129527641</v>
       </c>
-      <c r="K23" s="17">
+      <c r="K23" s="16">
         <v>68.478260869565219</v>
       </c>
-      <c r="L23" s="17">
+      <c r="L23" s="16">
         <v>71.739130434782609</v>
       </c>
     </row>
@@ -1372,7 +1351,7 @@
       <c r="B24" s="5">
         <v>7.1868583162217661</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="14" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="5">
@@ -1396,10 +1375,10 @@
       <c r="J24" s="6">
         <v>57.354330930786936</v>
       </c>
-      <c r="K24" s="17">
+      <c r="K24" s="16">
         <v>63.043478260869563</v>
       </c>
-      <c r="L24" s="17">
+      <c r="L24" s="16">
         <v>70.652173913043484</v>
       </c>
     </row>
@@ -1410,7 +1389,7 @@
       <c r="B25" s="5">
         <v>8.33949349760438</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="14" t="s">
         <v>2</v>
       </c>
       <c r="D25" s="5">
@@ -1434,10 +1413,10 @@
       <c r="J25" s="6">
         <v>63.14276788503593</v>
       </c>
-      <c r="K25" s="17">
+      <c r="K25" s="16">
         <v>69.565217391304344</v>
       </c>
-      <c r="L25" s="17">
+      <c r="L25" s="16">
         <v>78.260869565217391</v>
       </c>
     </row>
@@ -1448,7 +1427,7 @@
       <c r="B26" s="10">
         <v>13.44558521560575</v>
       </c>
-      <c r="C26" s="16" t="s">
+      <c r="C26" s="15" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="10">
@@ -1468,10 +1447,10 @@
         <v>25.518454361396248</v>
       </c>
       <c r="J26" s="11"/>
-      <c r="K26" s="20">
+      <c r="K26" s="19">
         <v>34.782608695652172</v>
       </c>
-      <c r="L26" s="20"/>
+      <c r="L26" s="19"/>
     </row>
     <row r="27" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
@@ -1480,7 +1459,7 @@
       <c r="B27" s="5">
         <v>18.387405886379192</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="14" t="s">
         <v>2</v>
       </c>
       <c r="D27" s="5">
@@ -1504,10 +1483,10 @@
       <c r="J27" s="1">
         <v>25.183949025259807</v>
       </c>
-      <c r="K27" s="17">
+      <c r="K27" s="16">
         <v>63.043478260869563</v>
       </c>
-      <c r="L27" s="17">
+      <c r="L27" s="16">
         <v>59.782608695652172</v>
       </c>
     </row>
@@ -1518,7 +1497,7 @@
       <c r="B28" s="10">
         <v>15.915126625598905</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="C28" s="15" t="s">
         <v>2</v>
       </c>
       <c r="D28" s="10">
@@ -1538,10 +1517,10 @@
         <v>21.592796573127025</v>
       </c>
       <c r="J28" s="11"/>
-      <c r="K28" s="20">
+      <c r="K28" s="19">
         <v>46.739130434782609</v>
       </c>
-      <c r="L28" s="20"/>
+      <c r="L28" s="19"/>
     </row>
     <row r="29" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
@@ -1550,7 +1529,7 @@
       <c r="B29" s="5">
         <v>19.879534565366189</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="C29" s="14" t="s">
         <v>2</v>
       </c>
       <c r="D29" s="5">
@@ -1574,10 +1553,10 @@
       <c r="J29" s="6">
         <v>35.636488239469358</v>
       </c>
-      <c r="K29" s="17">
+      <c r="K29" s="16">
         <v>71.739130434782609</v>
       </c>
-      <c r="L29" s="17">
+      <c r="L29" s="16">
         <v>80.434782608695656</v>
       </c>
     </row>
@@ -1585,42 +1564,40 @@
       <c r="I30" s="6"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
+      <c r="A33" s="12"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="12" t="s">
-        <v>7</v>
-      </c>
+      <c r="A34" s="12"/>
       <c r="B34" s="12"/>
       <c r="C34" s="12"/>
       <c r="D34" s="12"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>9</v>
-      </c>
+      <c r="A35" s="12"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>8</v>
-      </c>
+      <c r="A36" s="12"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="B37" s="21"/>
+      <c r="A37" s="12"/>
+      <c r="B37" s="12"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="B38" s="22"/>
+      <c r="A38" s="12"/>
+      <c r="B38" s="12"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/Marfan.xlsx
+++ b/data/Marfan.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chloe/Documents/Projet_ADM/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chloe/Documents/Laignel.Chloe/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0AA8FDA-7439-084B-B771-F12FC2BAC0C8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57291AAD-A724-D845-B874-409C04F3B853}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>

--- a/data/Marfan.xlsx
+++ b/data/Marfan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chloe/Documents/Laignel.Chloe/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57291AAD-A724-D845-B874-409C04F3B853}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91FCE054-3705-D249-B68F-F21B1ED4373A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="20">
   <si>
     <t>ID</t>
   </si>
@@ -67,6 +67,24 @@
   </si>
   <si>
     <t>PEDSQL_totalself_after</t>
+  </si>
+  <si>
+    <t>PEDSQL_santeself_after</t>
+  </si>
+  <si>
+    <t>PEDSQL_emotionself_after</t>
+  </si>
+  <si>
+    <t>PEDSQL_relationself_after</t>
+  </si>
+  <si>
+    <t>PEDSQL_ecoleself_after</t>
+  </si>
+  <si>
+    <t>PEDSQL_psycosocialself_after</t>
+  </si>
+  <si>
+    <t>PEDSQL_physiqueself_after</t>
   </si>
 </sst>
 </file>
@@ -111,7 +129,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -147,11 +165,29 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -206,6 +242,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -488,7 +536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:R38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="27.6640625" customWidth="1"/>
@@ -500,9 +548,15 @@
     <col min="10" max="10" width="27.83203125" customWidth="1"/>
     <col min="11" max="11" width="20.1640625" customWidth="1"/>
     <col min="12" max="12" width="21.1640625" customWidth="1"/>
+    <col min="13" max="13" width="24.5" customWidth="1"/>
+    <col min="14" max="14" width="26.83203125" customWidth="1"/>
+    <col min="15" max="15" width="21.1640625" customWidth="1"/>
+    <col min="16" max="16" width="25.33203125" customWidth="1"/>
+    <col min="17" max="17" width="26.33203125" customWidth="1"/>
+    <col min="18" max="18" width="25.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" ht="48" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -539,8 +593,26 @@
       <c r="L1" s="18" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="M1" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="O1" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="P1" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q1" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="R1" s="18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -577,8 +649,26 @@
       <c r="L2" s="16">
         <v>75</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M2" s="20">
+        <v>71.875</v>
+      </c>
+      <c r="N2" s="20">
+        <v>70</v>
+      </c>
+      <c r="O2" s="20">
+        <v>85</v>
+      </c>
+      <c r="P2" s="20">
+        <v>75</v>
+      </c>
+      <c r="Q2" s="20">
+        <v>76.666666666666671</v>
+      </c>
+      <c r="R2" s="20">
+        <v>71.875</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="9">
         <v>2</v>
       </c>
@@ -609,8 +699,14 @@
         <v>86.956521739130437</v>
       </c>
       <c r="L3" s="19"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M3" s="19"/>
+      <c r="N3" s="19"/>
+      <c r="O3" s="19"/>
+      <c r="P3" s="19"/>
+      <c r="Q3" s="19"/>
+      <c r="R3" s="19"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" s="9">
         <v>3</v>
       </c>
@@ -647,8 +743,26 @@
       <c r="L4" s="19">
         <v>92.391304347826093</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="M4" s="23">
+        <v>96.875</v>
+      </c>
+      <c r="N4" s="23">
+        <v>85</v>
+      </c>
+      <c r="O4" s="23">
+        <v>100</v>
+      </c>
+      <c r="P4" s="23">
+        <v>85</v>
+      </c>
+      <c r="Q4" s="23">
+        <v>90</v>
+      </c>
+      <c r="R4" s="23">
+        <v>96.875</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -685,8 +799,26 @@
       <c r="L5" s="16">
         <v>57.608695652173914</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M5" s="21">
+        <v>53.125</v>
+      </c>
+      <c r="N5" s="21">
+        <v>55</v>
+      </c>
+      <c r="O5" s="21">
+        <v>55</v>
+      </c>
+      <c r="P5" s="21">
+        <v>70</v>
+      </c>
+      <c r="Q5" s="21">
+        <v>60</v>
+      </c>
+      <c r="R5" s="21">
+        <v>53.125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="9">
         <v>5</v>
       </c>
@@ -719,8 +851,26 @@
       <c r="L6" s="19">
         <v>70.652173913043484</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="M6" s="23">
+        <v>53.125</v>
+      </c>
+      <c r="N6" s="23">
+        <v>65</v>
+      </c>
+      <c r="O6" s="23">
+        <v>75</v>
+      </c>
+      <c r="P6" s="23">
+        <v>100</v>
+      </c>
+      <c r="Q6" s="23">
+        <v>80</v>
+      </c>
+      <c r="R6" s="23">
+        <v>53.125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -757,8 +907,26 @@
       <c r="L7" s="16">
         <v>95.652173913043484</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M7" s="21">
+        <v>100</v>
+      </c>
+      <c r="N7" s="21">
+        <v>90</v>
+      </c>
+      <c r="O7" s="21">
+        <v>100</v>
+      </c>
+      <c r="P7" s="21">
+        <v>90</v>
+      </c>
+      <c r="Q7" s="21">
+        <v>93.333333333333329</v>
+      </c>
+      <c r="R7" s="21">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" s="9">
         <v>7</v>
       </c>
@@ -789,8 +957,14 @@
         <v>75</v>
       </c>
       <c r="L8" s="19"/>
-    </row>
-    <row r="9" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="M8" s="19"/>
+      <c r="N8" s="19"/>
+      <c r="O8" s="19"/>
+      <c r="P8" s="19"/>
+      <c r="Q8" s="19"/>
+      <c r="R8" s="19"/>
+    </row>
+    <row r="9" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -827,8 +1001,26 @@
       <c r="L9" s="16">
         <v>82.608695652173907</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="M9" s="21">
+        <v>100</v>
+      </c>
+      <c r="N9" s="21">
+        <v>75</v>
+      </c>
+      <c r="O9" s="21">
+        <v>85</v>
+      </c>
+      <c r="P9" s="21">
+        <v>60</v>
+      </c>
+      <c r="Q9" s="21">
+        <v>73.333333333333329</v>
+      </c>
+      <c r="R9" s="21">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -865,8 +1057,26 @@
       <c r="L10" s="16">
         <v>88.043478260869563</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="M10" s="21">
+        <v>90.625</v>
+      </c>
+      <c r="N10" s="21">
+        <v>85</v>
+      </c>
+      <c r="O10" s="21">
+        <v>90</v>
+      </c>
+      <c r="P10" s="21">
+        <v>85</v>
+      </c>
+      <c r="Q10" s="21">
+        <v>86.666666666666671</v>
+      </c>
+      <c r="R10" s="21">
+        <v>90.625</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -903,8 +1113,26 @@
       <c r="L11" s="16">
         <v>97.826086956521735</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="M11" s="21">
+        <v>96.875</v>
+      </c>
+      <c r="N11" s="21">
+        <v>100</v>
+      </c>
+      <c r="O11" s="21">
+        <v>100</v>
+      </c>
+      <c r="P11" s="21">
+        <v>95</v>
+      </c>
+      <c r="Q11" s="21">
+        <v>98.333333333333329</v>
+      </c>
+      <c r="R11" s="21">
+        <v>96.875</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -941,8 +1169,26 @@
       <c r="L12" s="16">
         <v>92.391304347826093</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="21">
+        <v>90.625</v>
+      </c>
+      <c r="N12" s="21">
+        <v>95</v>
+      </c>
+      <c r="O12" s="21">
+        <v>100</v>
+      </c>
+      <c r="P12" s="21">
+        <v>85</v>
+      </c>
+      <c r="Q12" s="21">
+        <v>93.333333333333329</v>
+      </c>
+      <c r="R12" s="21">
+        <v>90.625</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" s="9">
         <v>12</v>
       </c>
@@ -975,8 +1221,26 @@
       <c r="L13" s="19">
         <v>75</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="M13" s="23">
+        <v>78.125</v>
+      </c>
+      <c r="N13" s="23">
+        <v>65</v>
+      </c>
+      <c r="O13" s="23">
+        <v>75</v>
+      </c>
+      <c r="P13" s="23">
+        <v>80</v>
+      </c>
+      <c r="Q13" s="23">
+        <v>73.333333333333329</v>
+      </c>
+      <c r="R13" s="23">
+        <v>78.125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -1013,8 +1277,26 @@
       <c r="L14" s="16">
         <v>73.913043478260875</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="M14" s="21">
+        <v>65.625</v>
+      </c>
+      <c r="N14" s="21">
+        <v>85</v>
+      </c>
+      <c r="O14" s="21">
+        <v>75</v>
+      </c>
+      <c r="P14" s="21">
+        <v>75</v>
+      </c>
+      <c r="Q14" s="21">
+        <v>78.333333333333329</v>
+      </c>
+      <c r="R14" s="21">
+        <v>65.625</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -1051,8 +1333,26 @@
       <c r="L15" s="16">
         <v>72.826086956521735</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="M15" s="21">
+        <v>90.625</v>
+      </c>
+      <c r="N15" s="21">
+        <v>60</v>
+      </c>
+      <c r="O15" s="21">
+        <v>80</v>
+      </c>
+      <c r="P15" s="21">
+        <v>50</v>
+      </c>
+      <c r="Q15" s="21">
+        <v>63.333333333333336</v>
+      </c>
+      <c r="R15" s="21">
+        <v>90.625</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -1089,8 +1389,26 @@
       <c r="L16" s="16">
         <v>86.956521739130437</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="21">
+        <v>87.5</v>
+      </c>
+      <c r="N16" s="21">
+        <v>90</v>
+      </c>
+      <c r="O16" s="21">
+        <v>90</v>
+      </c>
+      <c r="P16" s="21">
+        <v>80</v>
+      </c>
+      <c r="Q16" s="21">
+        <v>86.666666666666671</v>
+      </c>
+      <c r="R16" s="21">
+        <v>87.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" s="9">
         <v>16</v>
       </c>
@@ -1121,8 +1439,14 @@
         <v>83.695652173913047</v>
       </c>
       <c r="L17" s="19"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="19"/>
+      <c r="N17" s="19"/>
+      <c r="O17" s="19"/>
+      <c r="P17" s="19"/>
+      <c r="Q17" s="19"/>
+      <c r="R17" s="19"/>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" s="9">
         <v>17</v>
       </c>
@@ -1153,8 +1477,14 @@
         <v>46.739130434782609</v>
       </c>
       <c r="L18" s="19"/>
-    </row>
-    <row r="19" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="M18" s="19"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="19"/>
+      <c r="P18" s="19"/>
+      <c r="Q18" s="19"/>
+      <c r="R18" s="19"/>
+    </row>
+    <row r="19" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -1191,8 +1521,26 @@
       <c r="L19" s="16">
         <v>77.173913043478265</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="M19" s="21">
+        <v>62.5</v>
+      </c>
+      <c r="N19" s="21">
+        <v>90</v>
+      </c>
+      <c r="O19" s="21">
+        <v>80</v>
+      </c>
+      <c r="P19" s="21">
+        <v>85</v>
+      </c>
+      <c r="Q19" s="21">
+        <v>85</v>
+      </c>
+      <c r="R19" s="21">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -1229,8 +1577,26 @@
       <c r="L20" s="16">
         <v>89.130434782608702</v>
       </c>
-    </row>
-    <row r="21" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="M20" s="21">
+        <v>93.75</v>
+      </c>
+      <c r="N20" s="21">
+        <v>100</v>
+      </c>
+      <c r="O20" s="21">
+        <v>80</v>
+      </c>
+      <c r="P20" s="21">
+        <v>80</v>
+      </c>
+      <c r="Q20" s="21">
+        <v>86.666666666666671</v>
+      </c>
+      <c r="R20" s="21">
+        <v>93.75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -1267,8 +1633,26 @@
       <c r="L21" s="16">
         <v>64.130434782608702</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="M21" s="21">
+        <v>75</v>
+      </c>
+      <c r="N21" s="21">
+        <v>40</v>
+      </c>
+      <c r="O21" s="21">
+        <v>80</v>
+      </c>
+      <c r="P21" s="21">
+        <v>55</v>
+      </c>
+      <c r="Q21" s="21">
+        <v>58.333333333333336</v>
+      </c>
+      <c r="R21" s="21">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>21</v>
       </c>
@@ -1305,8 +1689,26 @@
       <c r="L22" s="16">
         <v>83.695652173913047</v>
       </c>
-    </row>
-    <row r="23" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="M22" s="21">
+        <v>90.625</v>
+      </c>
+      <c r="N22" s="21">
+        <v>80</v>
+      </c>
+      <c r="O22" s="21">
+        <v>100</v>
+      </c>
+      <c r="P22" s="21">
+        <v>60</v>
+      </c>
+      <c r="Q22" s="21">
+        <v>80</v>
+      </c>
+      <c r="R22" s="21">
+        <v>90.625</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -1343,8 +1745,26 @@
       <c r="L23" s="16">
         <v>71.739130434782609</v>
       </c>
-    </row>
-    <row r="24" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="M23" s="21">
+        <v>71.875</v>
+      </c>
+      <c r="N23" s="21">
+        <v>75</v>
+      </c>
+      <c r="O23" s="21">
+        <v>70</v>
+      </c>
+      <c r="P23" s="21">
+        <v>70</v>
+      </c>
+      <c r="Q23" s="21">
+        <v>71.666666666666671</v>
+      </c>
+      <c r="R23" s="21">
+        <v>71.875</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>23</v>
       </c>
@@ -1381,8 +1801,26 @@
       <c r="L24" s="16">
         <v>70.652173913043484</v>
       </c>
-    </row>
-    <row r="25" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="M24" s="21">
+        <v>62.5</v>
+      </c>
+      <c r="N24" s="21">
+        <v>70</v>
+      </c>
+      <c r="O24" s="21">
+        <v>80</v>
+      </c>
+      <c r="P24" s="21">
+        <v>75</v>
+      </c>
+      <c r="Q24" s="21">
+        <v>75</v>
+      </c>
+      <c r="R24" s="21">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <v>24</v>
       </c>
@@ -1419,8 +1857,26 @@
       <c r="L25" s="16">
         <v>78.260869565217391</v>
       </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="21">
+        <v>93.75</v>
+      </c>
+      <c r="N25" s="21">
+        <v>70</v>
+      </c>
+      <c r="O25" s="21">
+        <v>100</v>
+      </c>
+      <c r="P25" s="21">
+        <v>40</v>
+      </c>
+      <c r="Q25" s="21">
+        <v>70</v>
+      </c>
+      <c r="R25" s="21">
+        <v>93.75</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" s="9">
         <v>25</v>
       </c>
@@ -1451,8 +1907,14 @@
         <v>34.782608695652172</v>
       </c>
       <c r="L26" s="19"/>
-    </row>
-    <row r="27" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="M26" s="19"/>
+      <c r="N26" s="19"/>
+      <c r="O26" s="19"/>
+      <c r="P26" s="19"/>
+      <c r="Q26" s="19"/>
+      <c r="R26" s="19"/>
+    </row>
+    <row r="27" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
         <v>26</v>
       </c>
@@ -1489,8 +1951,26 @@
       <c r="L27" s="16">
         <v>59.782608695652172</v>
       </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="21">
+        <v>65.625</v>
+      </c>
+      <c r="N27" s="21">
+        <v>55</v>
+      </c>
+      <c r="O27" s="21">
+        <v>65</v>
+      </c>
+      <c r="P27" s="21">
+        <v>50</v>
+      </c>
+      <c r="Q27" s="21">
+        <v>56.666666666666664</v>
+      </c>
+      <c r="R27" s="21">
+        <v>65.625</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A28" s="9">
         <v>27</v>
       </c>
@@ -1521,8 +2001,14 @@
         <v>46.739130434782609</v>
       </c>
       <c r="L28" s="19"/>
-    </row>
-    <row r="29" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="M28" s="19"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="19"/>
+      <c r="P28" s="19"/>
+      <c r="Q28" s="19"/>
+      <c r="R28" s="19"/>
+    </row>
+    <row r="29" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
         <v>28</v>
       </c>
@@ -1559,8 +2045,26 @@
       <c r="L29" s="16">
         <v>80.434782608695656</v>
       </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="22">
+        <v>68.75</v>
+      </c>
+      <c r="N29" s="22">
+        <v>90</v>
+      </c>
+      <c r="O29" s="22">
+        <v>80</v>
+      </c>
+      <c r="P29" s="22">
+        <v>90</v>
+      </c>
+      <c r="Q29" s="22">
+        <v>86.666666666666671</v>
+      </c>
+      <c r="R29" s="22">
+        <v>68.75</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
       <c r="I30" s="6"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">

--- a/data/Marfan.xlsx
+++ b/data/Marfan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chloe/Documents/Laignel.Chloe/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91FCE054-3705-D249-B68F-F21B1ED4373A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51262EF7-45F1-B344-A254-F6C4F2338791}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -556,7 +556,7 @@
     <col min="18" max="18" width="25.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="48" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>

--- a/data/Marfan.xlsx
+++ b/data/Marfan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chloe/Documents/Laignel.Chloe/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51262EF7-45F1-B344-A254-F6C4F2338791}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69B4B271-F8B1-174D-B925-07A27C92B7A0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="26">
   <si>
     <t>ID</t>
   </si>
@@ -86,6 +86,24 @@
   <si>
     <t>PEDSQL_physiqueself_after</t>
   </si>
+  <si>
+    <t>PEDSQL_santeself_before</t>
+  </si>
+  <si>
+    <t>PEDSQL_emotionself_before</t>
+  </si>
+  <si>
+    <t>PEDSQL_relationself_before</t>
+  </si>
+  <si>
+    <t>PEDSQL_ecoleself_before</t>
+  </si>
+  <si>
+    <t>PEDSQL_psycosocialself_before</t>
+  </si>
+  <si>
+    <t>PEDSQL_physiqueself_before</t>
+  </si>
 </sst>
 </file>
 
@@ -129,7 +147,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -165,29 +183,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -197,9 +197,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -224,9 +221,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -244,17 +238,12 @@
     <xf numFmtId="1" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -536,7 +525,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R38"/>
+  <dimension ref="A1:X38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="27.6640625" customWidth="1"/>
@@ -547,1393 +536,1861 @@
     <col min="9" max="9" width="28.1640625" customWidth="1"/>
     <col min="10" max="10" width="27.83203125" customWidth="1"/>
     <col min="11" max="11" width="20.1640625" customWidth="1"/>
-    <col min="12" max="12" width="21.1640625" customWidth="1"/>
-    <col min="13" max="13" width="24.5" customWidth="1"/>
-    <col min="14" max="14" width="26.83203125" customWidth="1"/>
-    <col min="15" max="15" width="21.1640625" customWidth="1"/>
-    <col min="16" max="16" width="25.33203125" customWidth="1"/>
-    <col min="17" max="17" width="26.33203125" customWidth="1"/>
-    <col min="18" max="18" width="25.5" customWidth="1"/>
+    <col min="12" max="13" width="21.1640625" customWidth="1"/>
+    <col min="14" max="15" width="24.5" customWidth="1"/>
+    <col min="16" max="17" width="26.83203125" customWidth="1"/>
+    <col min="18" max="19" width="21.1640625" customWidth="1"/>
+    <col min="20" max="21" width="25.33203125" customWidth="1"/>
+    <col min="22" max="23" width="26.33203125" customWidth="1"/>
+    <col min="24" max="24" width="25.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="K1" s="17" t="s">
+      <c r="K1" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="L1" s="18" t="s">
+      <c r="L1" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="M1" s="18" t="s">
+      <c r="M1" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="N1" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="N1" s="18" t="s">
+      <c r="O1" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="P1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="O1" s="18" t="s">
+      <c r="Q1" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="R1" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="P1" s="18" t="s">
+      <c r="S1" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="T1" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="Q1" s="18" t="s">
+      <c r="U1" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="V1" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="R1" s="18" t="s">
+      <c r="W1" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="X1" s="16" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:24" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="4">
         <v>10.529774127310061</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="4">
         <v>47.8</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="4">
         <v>162.6</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="4">
         <v>18.07951658852382</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G2" s="5">
         <v>660</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="5">
         <v>737</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="5">
         <v>29.918261704153004</v>
       </c>
-      <c r="J2" s="6">
+      <c r="J2" s="5">
         <v>39.958706632747109</v>
       </c>
-      <c r="K2" s="16">
+      <c r="K2" s="14">
         <v>69.565217391304344</v>
       </c>
-      <c r="L2" s="16">
-        <v>75</v>
-      </c>
-      <c r="M2" s="20">
+      <c r="L2" s="14">
+        <v>75</v>
+      </c>
+      <c r="M2" s="5">
+        <v>75</v>
+      </c>
+      <c r="N2" s="5">
         <v>71.875</v>
       </c>
-      <c r="N2" s="20">
+      <c r="O2" s="5">
+        <v>60</v>
+      </c>
+      <c r="P2" s="5">
         <v>70</v>
       </c>
-      <c r="O2" s="20">
+      <c r="Q2" s="5">
+        <v>65</v>
+      </c>
+      <c r="R2" s="5">
         <v>85</v>
       </c>
-      <c r="P2" s="20">
-        <v>75</v>
-      </c>
-      <c r="Q2" s="20">
+      <c r="S2" s="5">
+        <v>75</v>
+      </c>
+      <c r="T2" s="5">
+        <v>75</v>
+      </c>
+      <c r="U2" s="5">
+        <v>66.666666666666671</v>
+      </c>
+      <c r="V2" s="5">
         <v>76.666666666666671</v>
       </c>
-      <c r="R2" s="20">
+      <c r="W2" s="5">
+        <v>75</v>
+      </c>
+      <c r="X2" s="5">
         <v>71.875</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A3" s="9">
+    <row r="3" spans="1:24" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="8">
         <v>2</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="9">
         <v>14.351813826146476</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="9">
         <v>43</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="9">
         <v>174</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="9">
         <v>14.202668780552253</v>
       </c>
-      <c r="G3" s="11">
+      <c r="G3" s="10">
         <v>598</v>
       </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11">
+      <c r="H3" s="10"/>
+      <c r="I3" s="10">
         <v>38.74224312653152</v>
       </c>
-      <c r="J3" s="11"/>
-      <c r="K3" s="19">
+      <c r="J3" s="10"/>
+      <c r="K3" s="17">
         <v>86.956521739130437</v>
       </c>
-      <c r="L3" s="19"/>
-      <c r="M3" s="19"/>
-      <c r="N3" s="19"/>
-      <c r="O3" s="19"/>
-      <c r="P3" s="19"/>
-      <c r="Q3" s="19"/>
-      <c r="R3" s="19"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A4" s="9">
+      <c r="L3" s="17"/>
+      <c r="M3" s="10">
+        <v>87.5</v>
+      </c>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10">
+        <v>80</v>
+      </c>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10">
+        <v>85</v>
+      </c>
+      <c r="R3" s="10"/>
+      <c r="S3" s="10">
+        <v>95</v>
+      </c>
+      <c r="T3" s="10"/>
+      <c r="U3" s="10">
+        <v>86.666666666666671</v>
+      </c>
+      <c r="V3" s="10"/>
+      <c r="W3" s="10">
+        <v>87.5</v>
+      </c>
+      <c r="X3" s="10"/>
+    </row>
+    <row r="4" spans="1:24" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="8">
         <v>3</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="9">
         <v>10.704996577686517</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="9">
         <v>26</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="9">
         <v>142</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="9">
         <v>12.894267010513786</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="10">
         <v>556</v>
       </c>
-      <c r="H4" s="11">
+      <c r="H4" s="10">
         <v>618</v>
       </c>
-      <c r="I4" s="11">
+      <c r="I4" s="10">
         <v>38.237738985868674</v>
       </c>
-      <c r="J4" s="11">
+      <c r="J4" s="10">
         <v>41.531481990651635</v>
       </c>
-      <c r="K4" s="19">
+      <c r="K4" s="17">
         <v>92.391304347826093</v>
       </c>
-      <c r="L4" s="19">
+      <c r="L4" s="17">
         <v>92.391304347826093</v>
       </c>
-      <c r="M4" s="23">
+      <c r="M4" s="10">
         <v>96.875</v>
       </c>
-      <c r="N4" s="23">
+      <c r="N4" s="10">
+        <v>96.875</v>
+      </c>
+      <c r="O4" s="10">
         <v>85</v>
       </c>
-      <c r="O4" s="23">
+      <c r="P4" s="10">
+        <v>85</v>
+      </c>
+      <c r="Q4" s="10">
         <v>100</v>
       </c>
-      <c r="P4" s="23">
+      <c r="R4" s="10">
+        <v>100</v>
+      </c>
+      <c r="S4" s="10">
         <v>85</v>
       </c>
-      <c r="Q4" s="23">
+      <c r="T4" s="10">
+        <v>85</v>
+      </c>
+      <c r="U4" s="10">
         <v>90</v>
       </c>
-      <c r="R4" s="23">
+      <c r="V4" s="10">
+        <v>90</v>
+      </c>
+      <c r="W4" s="10">
         <v>96.875</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="X4" s="10">
+        <v>96.875</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="4">
         <v>17.393566050650239</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="4">
         <v>69</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="4">
         <v>185.5</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="4">
         <v>20.05216468930043</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="5">
         <v>588</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="5">
         <v>692</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="5">
         <v>28.950694773237657</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J5" s="5">
         <v>45.052754116732331</v>
       </c>
-      <c r="K5" s="16">
+      <c r="K5" s="14">
         <v>52.173913043478258</v>
       </c>
-      <c r="L5" s="16">
+      <c r="L5" s="14">
         <v>57.608695652173914</v>
       </c>
-      <c r="M5" s="21">
+      <c r="M5" s="5">
+        <v>46.875</v>
+      </c>
+      <c r="N5" s="5">
         <v>53.125</v>
       </c>
-      <c r="N5" s="21">
+      <c r="O5" s="5">
+        <v>50</v>
+      </c>
+      <c r="P5" s="5">
         <v>55</v>
       </c>
-      <c r="O5" s="21">
+      <c r="Q5" s="5">
+        <v>50</v>
+      </c>
+      <c r="R5" s="5">
         <v>55</v>
       </c>
-      <c r="P5" s="21">
+      <c r="S5" s="5">
+        <v>65</v>
+      </c>
+      <c r="T5" s="5">
         <v>70</v>
       </c>
-      <c r="Q5" s="21">
+      <c r="U5" s="5">
+        <v>55</v>
+      </c>
+      <c r="V5" s="5">
         <v>60</v>
       </c>
-      <c r="R5" s="21">
+      <c r="W5" s="5">
+        <v>46.875</v>
+      </c>
+      <c r="X5" s="5">
         <v>53.125</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A6" s="9">
+    <row r="6" spans="1:24" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="8">
         <v>5</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="9">
         <v>18.986995208761122</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="9">
         <v>54.8</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="9">
         <v>177</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="9">
         <v>17.491780778192727</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="10">
         <v>583</v>
       </c>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11">
+      <c r="H6" s="10"/>
+      <c r="I6" s="10">
         <v>39.959154936144614</v>
       </c>
-      <c r="J6" s="11"/>
-      <c r="K6" s="19">
+      <c r="J6" s="10"/>
+      <c r="K6" s="17">
         <v>76.086956521739125</v>
       </c>
-      <c r="L6" s="19">
+      <c r="L6" s="17">
         <v>70.652173913043484</v>
       </c>
-      <c r="M6" s="23">
+      <c r="M6" s="10">
+        <v>62.5</v>
+      </c>
+      <c r="N6" s="10">
         <v>53.125</v>
       </c>
-      <c r="N6" s="23">
+      <c r="O6" s="10">
+        <v>75</v>
+      </c>
+      <c r="P6" s="10">
         <v>65</v>
       </c>
-      <c r="O6" s="23">
-        <v>75</v>
-      </c>
-      <c r="P6" s="23">
+      <c r="Q6" s="10">
+        <v>75</v>
+      </c>
+      <c r="R6" s="10">
+        <v>75</v>
+      </c>
+      <c r="S6" s="10">
         <v>100</v>
       </c>
-      <c r="Q6" s="23">
+      <c r="T6" s="10">
+        <v>100</v>
+      </c>
+      <c r="U6" s="10">
+        <v>83.333333333333329</v>
+      </c>
+      <c r="V6" s="10">
         <v>80</v>
       </c>
-      <c r="R6" s="23">
+      <c r="W6" s="10">
+        <v>62.5</v>
+      </c>
+      <c r="X6" s="10">
         <v>53.125</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="4">
         <v>15.36208076659822</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="4">
         <v>66.599999999999994</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="4">
         <v>188</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="4">
         <v>18.843368039837031</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="5">
         <v>635</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="5">
         <v>697</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="5">
         <v>33.564402553634537</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="5">
         <v>52.530344959859711</v>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="14">
         <v>86.956521739130437</v>
       </c>
-      <c r="L7" s="16">
+      <c r="L7" s="14">
         <v>95.652173913043484</v>
       </c>
-      <c r="M7" s="21">
+      <c r="M7" s="5">
+        <v>93.75</v>
+      </c>
+      <c r="N7" s="5">
         <v>100</v>
       </c>
-      <c r="N7" s="21">
+      <c r="O7" s="5">
+        <v>70</v>
+      </c>
+      <c r="P7" s="5">
         <v>90</v>
       </c>
-      <c r="O7" s="21">
+      <c r="Q7" s="5">
+        <v>90</v>
+      </c>
+      <c r="R7" s="5">
         <v>100</v>
       </c>
-      <c r="P7" s="21">
+      <c r="S7" s="5">
         <v>90</v>
       </c>
-      <c r="Q7" s="21">
+      <c r="T7" s="5">
+        <v>90</v>
+      </c>
+      <c r="U7" s="5">
+        <v>83.333333333333329</v>
+      </c>
+      <c r="V7" s="5">
         <v>93.333333333333329</v>
       </c>
-      <c r="R7" s="21">
+      <c r="W7" s="5">
+        <v>93.75</v>
+      </c>
+      <c r="X7" s="5">
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A8" s="9">
+    <row r="8" spans="1:24" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="8">
         <v>7</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="9">
         <v>12.284736481861739</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="9">
         <v>35</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="9">
         <v>167</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="9">
         <v>12.549750797805586</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="10">
         <v>635</v>
       </c>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11">
+      <c r="H8" s="10"/>
+      <c r="I8" s="10">
         <v>32.16414908013607</v>
       </c>
-      <c r="J8" s="11"/>
-      <c r="K8" s="19">
-        <v>75</v>
-      </c>
-      <c r="L8" s="19"/>
-      <c r="M8" s="19"/>
-      <c r="N8" s="19"/>
-      <c r="O8" s="19"/>
-      <c r="P8" s="19"/>
-      <c r="Q8" s="19"/>
-      <c r="R8" s="19"/>
-    </row>
-    <row r="9" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="J8" s="10"/>
+      <c r="K8" s="17">
+        <v>75</v>
+      </c>
+      <c r="L8" s="17"/>
+      <c r="M8" s="10">
+        <v>75</v>
+      </c>
+      <c r="N8" s="10"/>
+      <c r="O8" s="10">
+        <v>95</v>
+      </c>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="10">
+        <v>55</v>
+      </c>
+      <c r="R8" s="10"/>
+      <c r="S8" s="10">
+        <v>75</v>
+      </c>
+      <c r="T8" s="10"/>
+      <c r="U8" s="10">
+        <v>75</v>
+      </c>
+      <c r="V8" s="10"/>
+      <c r="W8" s="10">
+        <v>75</v>
+      </c>
+      <c r="X8" s="10"/>
+    </row>
+    <row r="9" spans="1:24" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>8</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="4">
         <v>12.7419575633128</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="4">
         <v>53</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="4">
         <v>166</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="4">
         <v>19.233560749020178</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="5">
         <v>640</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="5">
         <v>598</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="5">
         <v>32.521836089946106</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="5">
         <v>36.911577069430813</v>
       </c>
-      <c r="K9" s="16">
+      <c r="K9" s="14">
         <v>66.304347826086953</v>
       </c>
-      <c r="L9" s="16">
+      <c r="L9" s="14">
         <v>82.608695652173907</v>
       </c>
-      <c r="M9" s="21">
+      <c r="M9" s="5">
+        <v>71.875</v>
+      </c>
+      <c r="N9" s="5">
         <v>100</v>
       </c>
-      <c r="N9" s="21">
-        <v>75</v>
-      </c>
-      <c r="O9" s="21">
+      <c r="O9" s="5">
+        <v>70</v>
+      </c>
+      <c r="P9" s="5">
+        <v>75</v>
+      </c>
+      <c r="Q9" s="5">
+        <v>70</v>
+      </c>
+      <c r="R9" s="5">
         <v>85</v>
       </c>
-      <c r="P9" s="21">
+      <c r="S9" s="5">
+        <v>50</v>
+      </c>
+      <c r="T9" s="5">
         <v>60</v>
       </c>
-      <c r="Q9" s="21">
+      <c r="U9" s="5">
+        <v>63.333333333333336</v>
+      </c>
+      <c r="V9" s="5">
         <v>73.333333333333329</v>
       </c>
-      <c r="R9" s="21">
+      <c r="W9" s="5">
+        <v>71.875</v>
+      </c>
+      <c r="X9" s="5">
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="4">
         <v>13.481177275838467</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="4">
         <v>55.3</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="4">
         <v>176</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="4">
         <v>17.852530991735538</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="5">
         <v>593</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="5">
         <v>682</v>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="5">
         <v>43.492806958849108</v>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="5">
         <v>47.335512358429426</v>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="14">
         <v>66.304347826086953</v>
       </c>
-      <c r="L10" s="16">
+      <c r="L10" s="14">
         <v>88.043478260869563</v>
       </c>
-      <c r="M10" s="21">
+      <c r="M10" s="5">
+        <v>78.125</v>
+      </c>
+      <c r="N10" s="5">
         <v>90.625</v>
       </c>
-      <c r="N10" s="21">
+      <c r="O10" s="5">
+        <v>55</v>
+      </c>
+      <c r="P10" s="5">
         <v>85</v>
       </c>
-      <c r="O10" s="21">
+      <c r="Q10" s="5">
+        <v>60</v>
+      </c>
+      <c r="R10" s="5">
         <v>90</v>
       </c>
-      <c r="P10" s="21">
+      <c r="S10" s="5">
+        <v>65</v>
+      </c>
+      <c r="T10" s="5">
         <v>85</v>
       </c>
-      <c r="Q10" s="21">
+      <c r="U10" s="5">
+        <v>60</v>
+      </c>
+      <c r="V10" s="5">
         <v>86.666666666666671</v>
       </c>
-      <c r="R10" s="21">
+      <c r="W10" s="5">
+        <v>78.125</v>
+      </c>
+      <c r="X10" s="5">
         <v>90.625</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="4">
         <v>11.321013004791238</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="4">
         <v>49</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="4">
         <v>165</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="4">
         <v>17.998163452708908</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="5">
         <v>551</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="5">
         <v>744</v>
       </c>
-      <c r="I11" s="6">
+      <c r="I11" s="5">
         <v>38.120064981676684</v>
       </c>
-      <c r="J11" s="6">
+      <c r="J11" s="5">
         <v>42.590756436910283</v>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="14">
         <v>92.391304347826093</v>
       </c>
-      <c r="L11" s="16">
+      <c r="L11" s="14">
         <v>97.826086956521735</v>
       </c>
-      <c r="M11" s="21">
+      <c r="M11" s="5">
+        <v>93.75</v>
+      </c>
+      <c r="N11" s="5">
         <v>96.875</v>
       </c>
-      <c r="N11" s="21">
+      <c r="O11" s="5">
+        <v>90</v>
+      </c>
+      <c r="P11" s="5">
         <v>100</v>
       </c>
-      <c r="O11" s="21">
+      <c r="Q11" s="5">
         <v>100</v>
       </c>
-      <c r="P11" s="21">
+      <c r="R11" s="5">
+        <v>100</v>
+      </c>
+      <c r="S11" s="5">
+        <v>85</v>
+      </c>
+      <c r="T11" s="5">
         <v>95</v>
       </c>
-      <c r="Q11" s="21">
+      <c r="U11" s="5">
+        <v>91.666666666666671</v>
+      </c>
+      <c r="V11" s="5">
         <v>98.333333333333329</v>
       </c>
-      <c r="R11" s="21">
+      <c r="W11" s="5">
+        <v>93.75</v>
+      </c>
+      <c r="X11" s="5">
         <v>96.875</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:24" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>11</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="4">
         <v>8.0876112251882279</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="4">
         <v>24</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="4">
         <v>134</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="4">
         <v>13.366005791935841</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="5">
         <v>516</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="5">
         <v>682</v>
       </c>
-      <c r="I12" s="6">
+      <c r="I12" s="5">
         <v>44.916283692522022</v>
       </c>
-      <c r="J12" s="6">
+      <c r="J12" s="5">
         <v>53.811381029549729</v>
       </c>
-      <c r="K12" s="16">
+      <c r="K12" s="14">
         <v>84.782608695652172</v>
       </c>
-      <c r="L12" s="16">
+      <c r="L12" s="14">
         <v>92.391304347826093</v>
       </c>
-      <c r="M12" s="21">
+      <c r="M12" s="5">
+        <v>87.5</v>
+      </c>
+      <c r="N12" s="5">
         <v>90.625</v>
       </c>
-      <c r="N12" s="21">
+      <c r="O12" s="5">
+        <v>85</v>
+      </c>
+      <c r="P12" s="5">
         <v>95</v>
       </c>
-      <c r="O12" s="21">
+      <c r="Q12" s="5">
+        <v>90</v>
+      </c>
+      <c r="R12" s="5">
         <v>100</v>
       </c>
-      <c r="P12" s="21">
+      <c r="S12" s="5">
+        <v>75</v>
+      </c>
+      <c r="T12" s="5">
         <v>85</v>
       </c>
-      <c r="Q12" s="21">
+      <c r="U12" s="5">
+        <v>83.333333333333329</v>
+      </c>
+      <c r="V12" s="5">
         <v>93.333333333333329</v>
       </c>
-      <c r="R12" s="21">
+      <c r="W12" s="5">
+        <v>87.5</v>
+      </c>
+      <c r="X12" s="5">
         <v>90.625</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A13" s="9">
+    <row r="13" spans="1:24" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="8">
         <v>12</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="9">
         <v>14.231348391512663</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="9">
         <v>62</v>
       </c>
-      <c r="E13" s="10">
+      <c r="E13" s="9">
         <v>171</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F13" s="9">
         <v>21.2</v>
       </c>
-      <c r="G13" s="11">
+      <c r="G13" s="10">
         <v>634</v>
       </c>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11">
+      <c r="H13" s="10"/>
+      <c r="I13" s="10">
         <v>56.480397155808568</v>
       </c>
-      <c r="J13" s="11"/>
-      <c r="K13" s="19">
+      <c r="J13" s="10"/>
+      <c r="K13" s="17">
         <v>91.304347826086953</v>
       </c>
-      <c r="L13" s="19">
-        <v>75</v>
-      </c>
-      <c r="M13" s="23">
+      <c r="L13" s="17">
+        <v>75</v>
+      </c>
+      <c r="M13" s="10">
+        <v>93.75</v>
+      </c>
+      <c r="N13" s="10">
         <v>78.125</v>
       </c>
-      <c r="N13" s="23">
+      <c r="O13" s="10">
+        <v>90</v>
+      </c>
+      <c r="P13" s="10">
         <v>65</v>
       </c>
-      <c r="O13" s="23">
-        <v>75</v>
-      </c>
-      <c r="P13" s="23">
+      <c r="Q13" s="10">
+        <v>90</v>
+      </c>
+      <c r="R13" s="10">
+        <v>75</v>
+      </c>
+      <c r="S13" s="10">
+        <v>90</v>
+      </c>
+      <c r="T13" s="10">
         <v>80</v>
       </c>
-      <c r="Q13" s="23">
+      <c r="U13" s="10">
+        <v>90</v>
+      </c>
+      <c r="V13" s="10">
         <v>73.333333333333329</v>
       </c>
-      <c r="R13" s="23">
+      <c r="W13" s="10">
+        <v>93.75</v>
+      </c>
+      <c r="X13" s="10">
         <v>78.125</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:24" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>13</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="4">
         <v>13.070499657768652</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="4">
         <v>43</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="4">
         <v>174</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="4">
         <v>14.202668780552253</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G14" s="5">
         <v>625</v>
       </c>
-      <c r="H14" s="6">
+      <c r="H14" s="5">
         <v>575</v>
       </c>
-      <c r="I14" s="6">
+      <c r="I14" s="5">
         <v>29.029602491827898</v>
       </c>
-      <c r="J14" s="6">
+      <c r="J14" s="5">
         <v>31.070821638848635</v>
       </c>
-      <c r="K14" s="16">
+      <c r="K14" s="14">
         <v>68.478260869565219</v>
       </c>
-      <c r="L14" s="16">
+      <c r="L14" s="14">
         <v>73.913043478260875</v>
       </c>
-      <c r="M14" s="21">
+      <c r="M14" s="5">
+        <v>50</v>
+      </c>
+      <c r="N14" s="5">
         <v>65.625</v>
       </c>
-      <c r="N14" s="21">
+      <c r="O14" s="5">
+        <v>75</v>
+      </c>
+      <c r="P14" s="5">
         <v>85</v>
       </c>
-      <c r="O14" s="21">
-        <v>75</v>
-      </c>
-      <c r="P14" s="21">
-        <v>75</v>
-      </c>
-      <c r="Q14" s="21">
+      <c r="Q14" s="5">
+        <v>70</v>
+      </c>
+      <c r="R14" s="5">
+        <v>75</v>
+      </c>
+      <c r="S14" s="5">
+        <v>90</v>
+      </c>
+      <c r="T14" s="5">
+        <v>75</v>
+      </c>
+      <c r="U14" s="5">
         <v>78.333333333333329</v>
       </c>
-      <c r="R14" s="21">
+      <c r="V14" s="5">
+        <v>78.333333333333329</v>
+      </c>
+      <c r="W14" s="5">
+        <v>50</v>
+      </c>
+      <c r="X14" s="5">
         <v>65.625</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>14</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15" s="4">
         <v>10.255989048596852</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="4">
         <v>32</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="4">
         <v>153</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="4">
         <v>13.669955999829126</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G15" s="5">
         <v>526</v>
       </c>
-      <c r="H15" s="6">
+      <c r="H15" s="5">
         <v>585</v>
       </c>
-      <c r="I15" s="6">
+      <c r="I15" s="5">
         <v>33.997268917455386</v>
       </c>
-      <c r="J15" s="6">
+      <c r="J15" s="5">
         <v>49.054142204827144</v>
       </c>
-      <c r="K15" s="16">
+      <c r="K15" s="14">
         <v>81.521739130434781</v>
       </c>
-      <c r="L15" s="16">
+      <c r="L15" s="14">
         <v>72.826086956521735</v>
       </c>
-      <c r="M15" s="21">
+      <c r="M15" s="5">
+        <v>84.375</v>
+      </c>
+      <c r="N15" s="5">
         <v>90.625</v>
       </c>
-      <c r="N15" s="21">
+      <c r="O15" s="5">
         <v>60</v>
       </c>
-      <c r="O15" s="21">
+      <c r="P15" s="5">
+        <v>60</v>
+      </c>
+      <c r="Q15" s="5">
+        <v>100</v>
+      </c>
+      <c r="R15" s="5">
         <v>80</v>
       </c>
-      <c r="P15" s="21">
+      <c r="S15" s="5">
+        <v>80</v>
+      </c>
+      <c r="T15" s="5">
         <v>50</v>
       </c>
-      <c r="Q15" s="21">
+      <c r="U15" s="5">
+        <v>80</v>
+      </c>
+      <c r="V15" s="5">
         <v>63.333333333333336</v>
       </c>
-      <c r="R15" s="21">
+      <c r="W15" s="5">
+        <v>84.375</v>
+      </c>
+      <c r="X15" s="5">
         <v>90.625</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>15</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16" s="4">
         <v>7.8631074606433948</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="4">
         <v>26</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="4">
         <v>142</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="4">
         <v>12.894267010513786</v>
       </c>
-      <c r="G16" s="6">
+      <c r="G16" s="5">
         <v>608</v>
       </c>
-      <c r="H16" s="6">
+      <c r="H16" s="5">
         <v>605</v>
       </c>
-      <c r="I16" s="6">
+      <c r="I16" s="5">
         <v>36.798248281734701</v>
       </c>
-      <c r="J16" s="6">
+      <c r="J16" s="5">
         <v>42.815507286224914</v>
       </c>
-      <c r="K16" s="16">
+      <c r="K16" s="14">
         <v>82.608695652173907</v>
       </c>
-      <c r="L16" s="16">
+      <c r="L16" s="14">
         <v>86.956521739130437</v>
       </c>
-      <c r="M16" s="21">
+      <c r="M16" s="5">
+        <v>93.75</v>
+      </c>
+      <c r="N16" s="5">
         <v>87.5</v>
       </c>
-      <c r="N16" s="21">
+      <c r="O16" s="5">
+        <v>60</v>
+      </c>
+      <c r="P16" s="5">
         <v>90</v>
       </c>
-      <c r="O16" s="21">
+      <c r="Q16" s="5">
+        <v>80</v>
+      </c>
+      <c r="R16" s="5">
         <v>90</v>
       </c>
-      <c r="P16" s="21">
+      <c r="S16" s="5">
+        <v>90</v>
+      </c>
+      <c r="T16" s="5">
         <v>80</v>
       </c>
-      <c r="Q16" s="21">
+      <c r="U16" s="5">
+        <v>76.666666666666671</v>
+      </c>
+      <c r="V16" s="5">
         <v>86.666666666666671</v>
       </c>
-      <c r="R16" s="21">
+      <c r="W16" s="5">
+        <v>93.75</v>
+      </c>
+      <c r="X16" s="5">
         <v>87.5</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A17" s="9">
+    <row r="17" spans="1:24" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="8">
         <v>16</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="9">
         <v>10.009582477754963</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="9">
         <v>32</v>
       </c>
-      <c r="E17" s="10">
+      <c r="E17" s="9">
         <v>150</v>
       </c>
-      <c r="F17" s="10">
+      <c r="F17" s="9">
         <v>14.222222222222221</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="10">
         <v>593</v>
       </c>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11">
+      <c r="H17" s="10"/>
+      <c r="I17" s="10">
         <v>40.46344303566898</v>
       </c>
-      <c r="J17" s="11"/>
-      <c r="K17" s="19">
+      <c r="J17" s="10"/>
+      <c r="K17" s="17">
         <v>83.695652173913047</v>
       </c>
-      <c r="L17" s="19"/>
-      <c r="M17" s="19"/>
-      <c r="N17" s="19"/>
-      <c r="O17" s="19"/>
-      <c r="P17" s="19"/>
-      <c r="Q17" s="19"/>
-      <c r="R17" s="19"/>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A18" s="9">
+      <c r="L17" s="17"/>
+      <c r="M17" s="10">
+        <v>84.375</v>
+      </c>
+      <c r="N17" s="10"/>
+      <c r="O17" s="10">
+        <v>80</v>
+      </c>
+      <c r="P17" s="10"/>
+      <c r="Q17" s="10">
+        <v>90</v>
+      </c>
+      <c r="R17" s="10"/>
+      <c r="S17" s="10">
+        <v>80</v>
+      </c>
+      <c r="T17" s="10"/>
+      <c r="U17" s="10">
+        <v>83.333333333333329</v>
+      </c>
+      <c r="V17" s="10"/>
+      <c r="W17" s="10">
+        <v>84.375</v>
+      </c>
+      <c r="X17" s="10"/>
+    </row>
+    <row r="18" spans="1:24" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="8">
         <v>17</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="9">
         <v>11.143052703627653</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="9">
         <v>62.7</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E18" s="9">
         <v>168</v>
       </c>
-      <c r="F18" s="10">
+      <c r="F18" s="9">
         <v>22.215136054421773</v>
       </c>
-      <c r="G18" s="11">
+      <c r="G18" s="10">
         <v>568</v>
       </c>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11">
+      <c r="H18" s="10"/>
+      <c r="I18" s="10">
         <v>38.62008136227815</v>
       </c>
-      <c r="J18" s="11"/>
-      <c r="K18" s="19">
+      <c r="J18" s="10"/>
+      <c r="K18" s="17">
         <v>46.739130434782609</v>
       </c>
-      <c r="L18" s="19"/>
-      <c r="M18" s="19"/>
-      <c r="N18" s="19"/>
-      <c r="O18" s="19"/>
-      <c r="P18" s="19"/>
-      <c r="Q18" s="19"/>
-      <c r="R18" s="19"/>
-    </row>
-    <row r="19" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="L18" s="17"/>
+      <c r="M18" s="10">
+        <v>65.625</v>
+      </c>
+      <c r="N18" s="10"/>
+      <c r="O18" s="10">
+        <v>40</v>
+      </c>
+      <c r="P18" s="10"/>
+      <c r="Q18" s="10">
+        <v>20</v>
+      </c>
+      <c r="R18" s="10"/>
+      <c r="S18" s="10">
+        <v>50</v>
+      </c>
+      <c r="T18" s="10"/>
+      <c r="U18" s="10">
+        <v>36.666666666666664</v>
+      </c>
+      <c r="V18" s="10"/>
+      <c r="W18" s="10">
+        <v>65.625</v>
+      </c>
+      <c r="X18" s="10"/>
+    </row>
+    <row r="19" spans="1:24" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>18</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B19" s="4">
         <v>17.130732375085557</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="C19" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D19" s="5">
+      <c r="D19" s="4">
         <v>54</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="4">
         <v>191</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F19" s="4">
         <v>14.802225816178286</v>
       </c>
-      <c r="G19" s="6">
+      <c r="G19" s="5">
         <v>620</v>
       </c>
-      <c r="H19" s="6">
+      <c r="H19" s="5">
         <v>615</v>
       </c>
-      <c r="I19" s="6">
+      <c r="I19" s="5">
         <v>23.522020896706785</v>
       </c>
-      <c r="J19" s="6">
+      <c r="J19" s="5">
         <v>25.568107528568813</v>
       </c>
-      <c r="K19" s="16">
+      <c r="K19" s="14">
         <v>65.217391304347828</v>
       </c>
-      <c r="L19" s="16">
+      <c r="L19" s="14">
         <v>77.173913043478265</v>
       </c>
-      <c r="M19" s="21">
+      <c r="M19" s="5">
+        <v>56.25</v>
+      </c>
+      <c r="N19" s="5">
         <v>62.5</v>
       </c>
-      <c r="N19" s="21">
+      <c r="O19" s="5">
+        <v>70</v>
+      </c>
+      <c r="P19" s="5">
         <v>90</v>
       </c>
-      <c r="O19" s="21">
+      <c r="Q19" s="5">
+        <v>75</v>
+      </c>
+      <c r="R19" s="5">
         <v>80</v>
       </c>
-      <c r="P19" s="21">
+      <c r="S19" s="5">
+        <v>65</v>
+      </c>
+      <c r="T19" s="5">
         <v>85</v>
       </c>
-      <c r="Q19" s="21">
+      <c r="U19" s="5">
+        <v>70</v>
+      </c>
+      <c r="V19" s="5">
         <v>85</v>
       </c>
-      <c r="R19" s="21">
+      <c r="W19" s="5">
+        <v>56.25</v>
+      </c>
+      <c r="X19" s="5">
         <v>62.5</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:24" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>19</v>
       </c>
-      <c r="B20" s="5">
+      <c r="B20" s="4">
         <v>7.8247775496235459</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C20" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D20" s="5">
+      <c r="D20" s="4">
         <v>22</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="4">
         <v>135</v>
       </c>
-      <c r="F20" s="5">
+      <c r="F20" s="4">
         <v>12.071330589849106</v>
       </c>
-      <c r="G20" s="6">
+      <c r="G20" s="5">
         <v>495</v>
       </c>
-      <c r="H20" s="6">
+      <c r="H20" s="5">
         <v>490</v>
       </c>
-      <c r="I20" s="6">
+      <c r="I20" s="5">
         <v>30.841300669339578</v>
       </c>
-      <c r="J20" s="6">
+      <c r="J20" s="5">
         <v>41.160007015287484</v>
       </c>
-      <c r="K20" s="16">
+      <c r="K20" s="14">
         <v>93.478260869565219</v>
       </c>
-      <c r="L20" s="16">
+      <c r="L20" s="14">
         <v>89.130434782608702</v>
       </c>
-      <c r="M20" s="21">
+      <c r="M20" s="5">
+        <v>96.875</v>
+      </c>
+      <c r="N20" s="5">
         <v>93.75</v>
       </c>
-      <c r="N20" s="21">
+      <c r="O20" s="5">
         <v>100</v>
       </c>
-      <c r="O20" s="21">
+      <c r="P20" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q20" s="5">
         <v>80</v>
       </c>
-      <c r="P20" s="21">
+      <c r="R20" s="5">
         <v>80</v>
       </c>
-      <c r="Q20" s="21">
+      <c r="S20" s="5">
+        <v>95</v>
+      </c>
+      <c r="T20" s="5">
+        <v>80</v>
+      </c>
+      <c r="U20" s="5">
+        <v>91.666666666666671</v>
+      </c>
+      <c r="V20" s="5">
         <v>86.666666666666671</v>
       </c>
-      <c r="R20" s="21">
+      <c r="W20" s="5">
+        <v>96.875</v>
+      </c>
+      <c r="X20" s="5">
         <v>93.75</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:24" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>20</v>
       </c>
-      <c r="B21" s="5">
+      <c r="B21" s="4">
         <v>10.250513347022586</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="C21" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D21" s="5">
+      <c r="D21" s="4">
         <v>29</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E21" s="4">
         <v>147</v>
       </c>
-      <c r="F21" s="5">
+      <c r="F21" s="4">
         <v>13.420334120042575</v>
       </c>
-      <c r="G21" s="6">
+      <c r="G21" s="5">
         <v>650</v>
       </c>
-      <c r="H21" s="6">
+      <c r="H21" s="5">
         <v>725</v>
       </c>
-      <c r="I21" s="6">
+      <c r="I21" s="5">
         <v>34.423500349068263</v>
       </c>
-      <c r="J21" s="6">
+      <c r="J21" s="5">
         <v>46.919406966603397</v>
       </c>
-      <c r="K21" s="16">
+      <c r="K21" s="14">
         <v>60.869565217391305</v>
       </c>
-      <c r="L21" s="16">
+      <c r="L21" s="14">
         <v>64.130434782608702</v>
       </c>
-      <c r="M21" s="21">
-        <v>75</v>
-      </c>
-      <c r="N21" s="21">
+      <c r="M21" s="5">
+        <v>62.5</v>
+      </c>
+      <c r="N21" s="5">
+        <v>75</v>
+      </c>
+      <c r="O21" s="5">
+        <v>45</v>
+      </c>
+      <c r="P21" s="5">
         <v>40</v>
       </c>
-      <c r="O21" s="21">
+      <c r="Q21" s="5">
+        <v>75</v>
+      </c>
+      <c r="R21" s="5">
         <v>80</v>
       </c>
-      <c r="P21" s="21">
+      <c r="S21" s="5">
+        <v>60</v>
+      </c>
+      <c r="T21" s="5">
         <v>55</v>
       </c>
-      <c r="Q21" s="21">
+      <c r="U21" s="5">
+        <v>60</v>
+      </c>
+      <c r="V21" s="5">
         <v>58.333333333333336</v>
       </c>
-      <c r="R21" s="21">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="W21" s="5">
+        <v>62.5</v>
+      </c>
+      <c r="X21" s="5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>21</v>
       </c>
-      <c r="B22" s="5">
+      <c r="B22" s="4">
         <v>11.047227926078028</v>
       </c>
-      <c r="C22" s="14" t="s">
+      <c r="C22" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D22" s="4">
         <v>54</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E22" s="4">
         <v>165</v>
       </c>
-      <c r="F22" s="5">
+      <c r="F22" s="4">
         <v>19.834710743801654</v>
       </c>
-      <c r="G22" s="6">
+      <c r="G22" s="5">
         <v>580</v>
       </c>
-      <c r="H22" s="6">
+      <c r="H22" s="5">
         <v>540</v>
       </c>
-      <c r="I22" s="6">
+      <c r="I22" s="5">
         <v>32.150817937965172</v>
       </c>
-      <c r="J22" s="6">
+      <c r="J22" s="5">
         <v>39.779845152280622</v>
       </c>
-      <c r="K22" s="16">
+      <c r="K22" s="14">
         <v>68.478260869565219</v>
       </c>
-      <c r="L22" s="16">
+      <c r="L22" s="14">
         <v>83.695652173913047</v>
       </c>
-      <c r="M22" s="21">
+      <c r="M22" s="5">
+        <v>78.125</v>
+      </c>
+      <c r="N22" s="5">
         <v>90.625</v>
       </c>
-      <c r="N22" s="21">
+      <c r="O22" s="5">
+        <v>70</v>
+      </c>
+      <c r="P22" s="5">
         <v>80</v>
       </c>
-      <c r="O22" s="21">
+      <c r="Q22" s="5">
+        <v>50</v>
+      </c>
+      <c r="R22" s="5">
         <v>100</v>
       </c>
-      <c r="P22" s="21">
+      <c r="S22" s="5">
+        <v>70</v>
+      </c>
+      <c r="T22" s="5">
         <v>60</v>
       </c>
-      <c r="Q22" s="21">
+      <c r="U22" s="5">
+        <v>63.333333333333336</v>
+      </c>
+      <c r="V22" s="5">
         <v>80</v>
       </c>
-      <c r="R22" s="21">
+      <c r="W22" s="5">
+        <v>78.125</v>
+      </c>
+      <c r="X22" s="5">
         <v>90.625</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:24" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>22</v>
       </c>
-      <c r="B23" s="5">
+      <c r="B23" s="4">
         <v>17.828884325804243</v>
       </c>
-      <c r="C23" s="14" t="s">
+      <c r="C23" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D23" s="5">
+      <c r="D23" s="4">
         <v>82</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E23" s="4">
         <v>183</v>
       </c>
-      <c r="F23" s="5">
+      <c r="F23" s="4">
         <v>24.485652005136011</v>
       </c>
-      <c r="G23" s="6">
+      <c r="G23" s="5">
         <v>560</v>
       </c>
-      <c r="H23" s="6">
+      <c r="H23" s="5">
         <v>625</v>
       </c>
-      <c r="I23" s="6">
+      <c r="I23" s="5">
         <v>28.469854591019029</v>
       </c>
-      <c r="J23" s="6">
+      <c r="J23" s="5">
         <v>39.362415129527641</v>
       </c>
-      <c r="K23" s="16">
+      <c r="K23" s="14">
         <v>68.478260869565219</v>
       </c>
-      <c r="L23" s="16">
+      <c r="L23" s="14">
         <v>71.739130434782609</v>
       </c>
-      <c r="M23" s="21">
+      <c r="M23" s="5">
         <v>71.875</v>
       </c>
-      <c r="N23" s="21">
-        <v>75</v>
-      </c>
-      <c r="O23" s="21">
+      <c r="N23" s="5">
+        <v>71.875</v>
+      </c>
+      <c r="O23" s="5">
+        <v>75</v>
+      </c>
+      <c r="P23" s="5">
+        <v>75</v>
+      </c>
+      <c r="Q23" s="5">
         <v>70</v>
       </c>
-      <c r="P23" s="21">
+      <c r="R23" s="5">
         <v>70</v>
       </c>
-      <c r="Q23" s="21">
+      <c r="S23" s="5">
+        <v>55</v>
+      </c>
+      <c r="T23" s="5">
+        <v>70</v>
+      </c>
+      <c r="U23" s="5">
+        <v>66.666666666666671</v>
+      </c>
+      <c r="V23" s="5">
         <v>71.666666666666671</v>
       </c>
-      <c r="R23" s="21">
+      <c r="W23" s="5">
         <v>71.875</v>
       </c>
-    </row>
-    <row r="24" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="X23" s="5">
+        <v>71.875</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>23</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B24" s="4">
         <v>7.1868583162217661</v>
       </c>
-      <c r="C24" s="14" t="s">
+      <c r="C24" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D24" s="5">
+      <c r="D24" s="4">
         <v>28</v>
       </c>
-      <c r="E24" s="5">
+      <c r="E24" s="4">
         <v>138</v>
       </c>
-      <c r="F24" s="5">
+      <c r="F24" s="4">
         <v>14.702793530770849</v>
       </c>
-      <c r="G24" s="6">
+      <c r="G24" s="5">
         <v>450</v>
       </c>
-      <c r="H24" s="6">
+      <c r="H24" s="5">
         <v>460</v>
       </c>
-      <c r="I24" s="6">
+      <c r="I24" s="5">
         <v>39.562601767164615</v>
       </c>
-      <c r="J24" s="6">
+      <c r="J24" s="5">
         <v>57.354330930786936</v>
       </c>
-      <c r="K24" s="16">
+      <c r="K24" s="14">
         <v>63.043478260869563</v>
       </c>
-      <c r="L24" s="16">
+      <c r="L24" s="14">
         <v>70.652173913043484</v>
       </c>
-      <c r="M24" s="21">
+      <c r="M24" s="5">
+        <v>56.25</v>
+      </c>
+      <c r="N24" s="5">
         <v>62.5</v>
       </c>
-      <c r="N24" s="21">
+      <c r="O24" s="5">
         <v>70</v>
       </c>
-      <c r="O24" s="21">
+      <c r="P24" s="5">
+        <v>70</v>
+      </c>
+      <c r="Q24" s="5">
+        <v>70</v>
+      </c>
+      <c r="R24" s="5">
         <v>80</v>
       </c>
-      <c r="P24" s="21">
-        <v>75</v>
-      </c>
-      <c r="Q24" s="21">
-        <v>75</v>
-      </c>
-      <c r="R24" s="21">
+      <c r="S24" s="5">
+        <v>60</v>
+      </c>
+      <c r="T24" s="5">
+        <v>75</v>
+      </c>
+      <c r="U24" s="5">
+        <v>66.666666666666671</v>
+      </c>
+      <c r="V24" s="5">
+        <v>75</v>
+      </c>
+      <c r="W24" s="5">
+        <v>56.25</v>
+      </c>
+      <c r="X24" s="5">
         <v>62.5</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:24" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <v>24</v>
       </c>
-      <c r="B25" s="5">
+      <c r="B25" s="4">
         <v>8.33949349760438</v>
       </c>
-      <c r="C25" s="14" t="s">
+      <c r="C25" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D25" s="5">
+      <c r="D25" s="4">
         <v>27</v>
       </c>
-      <c r="E25" s="5">
+      <c r="E25" s="4">
         <v>136</v>
       </c>
-      <c r="F25" s="5">
+      <c r="F25" s="4">
         <v>14.5977508650519</v>
       </c>
-      <c r="G25" s="6">
+      <c r="G25" s="5">
         <v>560</v>
       </c>
-      <c r="H25" s="6">
+      <c r="H25" s="5">
         <v>530</v>
       </c>
-      <c r="I25" s="6">
+      <c r="I25" s="5">
         <v>52.151898734177216</v>
       </c>
-      <c r="J25" s="6">
+      <c r="J25" s="5">
         <v>63.14276788503593</v>
       </c>
-      <c r="K25" s="16">
+      <c r="K25" s="14">
         <v>69.565217391304344</v>
       </c>
-      <c r="L25" s="16">
+      <c r="L25" s="14">
         <v>78.260869565217391</v>
       </c>
-      <c r="M25" s="21">
+      <c r="M25" s="5">
+        <v>71.875</v>
+      </c>
+      <c r="N25" s="5">
         <v>93.75</v>
       </c>
-      <c r="N25" s="21">
+      <c r="O25" s="5">
+        <v>80</v>
+      </c>
+      <c r="P25" s="5">
         <v>70</v>
       </c>
-      <c r="O25" s="21">
+      <c r="Q25" s="5">
         <v>100</v>
       </c>
-      <c r="P25" s="21">
+      <c r="R25" s="5">
+        <v>100</v>
+      </c>
+      <c r="S25" s="5">
+        <v>25</v>
+      </c>
+      <c r="T25" s="5">
         <v>40</v>
       </c>
-      <c r="Q25" s="21">
+      <c r="U25" s="5">
+        <v>68.333333333333329</v>
+      </c>
+      <c r="V25" s="5">
         <v>70</v>
       </c>
-      <c r="R25" s="21">
+      <c r="W25" s="5">
+        <v>71.875</v>
+      </c>
+      <c r="X25" s="5">
         <v>93.75</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A26" s="9">
+    <row r="26" spans="1:24" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="8">
         <v>25</v>
       </c>
-      <c r="B26" s="10">
+      <c r="B26" s="9">
         <v>13.44558521560575</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C26" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D26" s="10">
+      <c r="D26" s="9">
         <v>42</v>
       </c>
-      <c r="E26" s="10">
+      <c r="E26" s="9">
         <v>182</v>
       </c>
-      <c r="F26" s="10">
+      <c r="F26" s="9">
         <v>12.679628064243447</v>
       </c>
-      <c r="G26" s="11">
+      <c r="G26" s="10">
         <v>580</v>
       </c>
-      <c r="H26" s="11"/>
-      <c r="I26" s="11">
+      <c r="H26" s="10"/>
+      <c r="I26" s="10">
         <v>25.518454361396248</v>
       </c>
-      <c r="J26" s="11"/>
-      <c r="K26" s="19">
+      <c r="J26" s="10"/>
+      <c r="K26" s="17">
         <v>34.782608695652172</v>
       </c>
-      <c r="L26" s="19"/>
-      <c r="M26" s="19"/>
-      <c r="N26" s="19"/>
-      <c r="O26" s="19"/>
-      <c r="P26" s="19"/>
-      <c r="Q26" s="19"/>
-      <c r="R26" s="19"/>
-    </row>
-    <row r="27" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="L26" s="17"/>
+      <c r="M26" s="10">
+        <v>37.5</v>
+      </c>
+      <c r="N26" s="10"/>
+      <c r="O26" s="10">
+        <v>35</v>
+      </c>
+      <c r="P26" s="10"/>
+      <c r="Q26" s="10">
+        <v>35</v>
+      </c>
+      <c r="R26" s="10"/>
+      <c r="S26" s="10">
+        <v>30</v>
+      </c>
+      <c r="T26" s="10"/>
+      <c r="U26" s="10">
+        <v>33.333333333333336</v>
+      </c>
+      <c r="V26" s="10"/>
+      <c r="W26" s="10">
+        <v>37.5</v>
+      </c>
+      <c r="X26" s="10"/>
+    </row>
+    <row r="27" spans="1:24" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
         <v>26</v>
       </c>
-      <c r="B27" s="5">
+      <c r="B27" s="4">
         <v>18.387405886379192</v>
       </c>
-      <c r="C27" s="14" t="s">
+      <c r="C27" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D27" s="5">
+      <c r="D27" s="4">
         <v>58.5</v>
       </c>
-      <c r="E27" s="5">
+      <c r="E27" s="4">
         <v>196</v>
       </c>
-      <c r="F27" s="5">
+      <c r="F27" s="4">
         <v>15.228029987505208</v>
       </c>
-      <c r="G27" s="6">
+      <c r="G27" s="5">
         <v>535</v>
       </c>
       <c r="H27" s="1">
@@ -1945,163 +2402,217 @@
       <c r="J27" s="1">
         <v>25.183949025259807</v>
       </c>
-      <c r="K27" s="16">
+      <c r="K27" s="14">
         <v>63.043478260869563</v>
       </c>
-      <c r="L27" s="16">
+      <c r="L27" s="14">
         <v>59.782608695652172</v>
       </c>
-      <c r="M27" s="21">
+      <c r="M27" s="1">
+        <v>62.5</v>
+      </c>
+      <c r="N27" s="1">
         <v>65.625</v>
       </c>
-      <c r="N27" s="21">
+      <c r="O27" s="1">
+        <v>60</v>
+      </c>
+      <c r="P27" s="1">
         <v>55</v>
       </c>
-      <c r="O27" s="21">
+      <c r="Q27" s="1">
+        <v>60</v>
+      </c>
+      <c r="R27" s="1">
         <v>65</v>
       </c>
-      <c r="P27" s="21">
+      <c r="S27" s="1">
+        <v>70</v>
+      </c>
+      <c r="T27" s="1">
         <v>50</v>
       </c>
-      <c r="Q27" s="21">
+      <c r="U27" s="1">
+        <v>63.333333333333336</v>
+      </c>
+      <c r="V27" s="1">
         <v>56.666666666666664</v>
       </c>
-      <c r="R27" s="21">
+      <c r="W27" s="1">
+        <v>62.5</v>
+      </c>
+      <c r="X27" s="1">
         <v>65.625</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A28" s="9">
+    <row r="28" spans="1:24" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="8">
         <v>27</v>
       </c>
-      <c r="B28" s="10">
+      <c r="B28" s="9">
         <v>15.915126625598905</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D28" s="10">
+      <c r="D28" s="9">
         <v>71</v>
       </c>
-      <c r="E28" s="10">
+      <c r="E28" s="9">
         <v>183</v>
       </c>
-      <c r="F28" s="10">
+      <c r="F28" s="9">
         <v>21.200991370300692</v>
       </c>
-      <c r="G28" s="11">
+      <c r="G28" s="10">
         <v>588</v>
       </c>
-      <c r="H28" s="11"/>
-      <c r="I28" s="11">
+      <c r="H28" s="10"/>
+      <c r="I28" s="10">
         <v>21.592796573127025</v>
       </c>
-      <c r="J28" s="11"/>
-      <c r="K28" s="19">
+      <c r="J28" s="10"/>
+      <c r="K28" s="17">
         <v>46.739130434782609</v>
       </c>
-      <c r="L28" s="19"/>
-      <c r="M28" s="19"/>
-      <c r="N28" s="19"/>
-      <c r="O28" s="19"/>
-      <c r="P28" s="19"/>
-      <c r="Q28" s="19"/>
-      <c r="R28" s="19"/>
-    </row>
-    <row r="29" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="L28" s="17"/>
+      <c r="M28" s="10">
+        <v>56.25</v>
+      </c>
+      <c r="N28" s="10"/>
+      <c r="O28" s="10">
+        <v>45</v>
+      </c>
+      <c r="P28" s="10"/>
+      <c r="Q28" s="10">
+        <v>30</v>
+      </c>
+      <c r="R28" s="10"/>
+      <c r="S28" s="10">
+        <v>50</v>
+      </c>
+      <c r="T28" s="10"/>
+      <c r="U28" s="10">
+        <v>41.666666666666664</v>
+      </c>
+      <c r="V28" s="10"/>
+      <c r="W28" s="10">
+        <v>56.25</v>
+      </c>
+      <c r="X28" s="10"/>
+    </row>
+    <row r="29" spans="1:24" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
         <v>28</v>
       </c>
-      <c r="B29" s="5">
+      <c r="B29" s="4">
         <v>19.879534565366189</v>
       </c>
-      <c r="C29" s="14" t="s">
+      <c r="C29" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D29" s="5">
+      <c r="D29" s="4">
         <v>65</v>
       </c>
-      <c r="E29" s="5">
+      <c r="E29" s="4">
         <v>199</v>
       </c>
-      <c r="F29" s="5">
+      <c r="F29" s="4">
         <v>16.413726926087726</v>
       </c>
-      <c r="G29" s="6">
+      <c r="G29" s="5">
         <v>600</v>
       </c>
-      <c r="H29" s="6">
+      <c r="H29" s="5">
         <v>595</v>
       </c>
-      <c r="I29" s="6">
+      <c r="I29" s="5">
         <v>27.123241227326673</v>
       </c>
-      <c r="J29" s="6">
+      <c r="J29" s="5">
         <v>35.636488239469358</v>
       </c>
-      <c r="K29" s="16">
+      <c r="K29" s="14">
         <v>71.739130434782609</v>
       </c>
-      <c r="L29" s="16">
+      <c r="L29" s="14">
         <v>80.434782608695656</v>
       </c>
-      <c r="M29" s="22">
+      <c r="M29" s="5">
+        <v>56.25</v>
+      </c>
+      <c r="N29" s="5">
         <v>68.75</v>
       </c>
-      <c r="N29" s="22">
+      <c r="O29" s="5">
+        <v>80</v>
+      </c>
+      <c r="P29" s="5">
         <v>90</v>
       </c>
-      <c r="O29" s="22">
+      <c r="Q29" s="5">
+        <v>75</v>
+      </c>
+      <c r="R29" s="5">
         <v>80</v>
       </c>
-      <c r="P29" s="22">
+      <c r="S29" s="5">
+        <v>85</v>
+      </c>
+      <c r="T29" s="5">
         <v>90</v>
       </c>
-      <c r="Q29" s="22">
+      <c r="U29" s="5">
+        <v>80</v>
+      </c>
+      <c r="V29" s="5">
         <v>86.666666666666671</v>
       </c>
-      <c r="R29" s="22">
+      <c r="W29" s="5">
+        <v>56.25</v>
+      </c>
+      <c r="X29" s="5">
         <v>68.75</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="I30" s="6"/>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="I30" s="5"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="12"/>
-      <c r="B33" s="12"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
+      <c r="A33" s="11"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="12"/>
-      <c r="B34" s="12"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
+      <c r="A34" s="11"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="12"/>
-      <c r="B35" s="12"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="12"/>
+      <c r="A35" s="11"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="12"/>
-      <c r="B36" s="12"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
+      <c r="A36" s="11"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="12"/>
-      <c r="B37" s="12"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="12"/>
+      <c r="A37" s="11"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="12"/>
-      <c r="B38" s="12"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="12"/>
+      <c r="A38" s="11"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
